--- a/data/trans_dic/P19C11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,96</t>
+          <t>2,81; 5,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,11</t>
+          <t>2,94; 5,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,05</t>
+          <t>3,21; 4,96</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,65</t>
+          <t>2,49; 4,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,28</t>
+          <t>2,48; 4,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,28</t>
+          <t>2,81; 4,22</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 8,1</t>
+          <t>4,45; 8,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,6</t>
+          <t>3,97; 6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,82</t>
+          <t>4,63; 6,87</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,03</t>
+          <t>3,16; 4,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,51</t>
+          <t>3,13; 4,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,5</t>
+          <t>3,47; 4,52</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por implantes / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13503; 28893</t>
+          <t>13615; 28897</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21050; 36901</t>
+          <t>21250; 36606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39485; 60859</t>
+          <t>38766; 59879</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57683; 103726</t>
+          <t>55615; 103929</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54573; 94169</t>
+          <t>54485; 94847</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124132; 189615</t>
+          <t>124531; 187074</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28634; 51150</t>
+          <t>28102; 51357</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25116; 43031</t>
+          <t>25888; 43487</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59427; 87553</t>
+          <t>59358; 88199</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>109835; 168281</t>
+          <t>105650; 163669</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>111053; 160887</t>
+          <t>111952; 158272</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>236224; 311272</t>
+          <t>240205; 312849</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C11_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,96</t>
+          <t>2,88; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,07</t>
+          <t>2,98; 5,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,96</t>
+          <t>3,22; 4,97</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,66</t>
+          <t>3,35; 5,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,32</t>
+          <t>3,26; 4,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,22</t>
+          <t>3,54; 4,65</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,13</t>
+          <t>4,59; 8,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,67</t>
+          <t>3,91; 6,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,87</t>
+          <t>4,5; 6,83</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,89</t>
+          <t>3,82; 5,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,43</t>
+          <t>3,69; 4,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,52</t>
+          <t>3,93; 4,85</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>53722</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13615; 28897</t>
+          <t>15485; 31909</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21250; 36606</t>
+          <t>23397; 39720</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38766; 59879</t>
+          <t>42529; 65654</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>89900</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76000</t>
+          <t>82645</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157163</t>
+          <t>172545</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55615; 103929</t>
+          <t>71803; 111051</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54485; 94847</t>
+          <t>68873; 98034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124531; 187074</t>
+          <t>150493; 198139</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39007</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33467</t>
+          <t>37344</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72474</t>
+          <t>79809</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28102; 51357</t>
+          <t>32248; 57366</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25888; 43487</t>
+          <t>28327; 48120</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59358; 88199</t>
+          <t>64245; 97467</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>137732</t>
+          <t>150814</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278406</t>
+          <t>306076</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105650; 163669</t>
+          <t>129219; 179618</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>111952; 158272</t>
+          <t>133450; 172604</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>240205; 312849</t>
+          <t>275551; 339658</t>
         </is>
       </c>
     </row>
